--- a/research/sovereign-ai/sovereign-ai-model.xlsx
+++ b/research/sovereign-ai/sovereign-ai-model.xlsx
@@ -1326,7 +1326,7 @@
     <t xml:space="preserve">My estimate.</t>
   </si>
   <si>
-    <t xml:space="preserve">Canada Sovereign AI Compute Strategy (CAD 2B) and Australia (Firmus $10B facility)</t>
+    <t xml:space="preserve">Canada Sovereign AI Compute Strategy (CAD 2B) and Australia (Firmus $10B debt facility)</t>
   </si>
   <si>
     <t xml:space="preserve">Canada/Australia</t>
